--- a/data/trans_camb/IP26C_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 13,0</t>
+          <t>-5,46; 11,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 16,67</t>
+          <t>-3,86; 15,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,7; -2,24</t>
+          <t>-14,84; -2,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 10,09</t>
+          <t>-7,6; 11,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 1,92</t>
+          <t>-13,77; 1,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,54; -0,47</t>
+          <t>-14,89; 0,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 8,47</t>
+          <t>-5,28; 8,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 5,83</t>
+          <t>-6,21; 5,2</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,62; -2,65</t>
+          <t>-12,96; -2,84</t>
         </is>
       </c>
     </row>
@@ -783,54 +783,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,48; 293,58</t>
+          <t>-48,91; 266,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-28,13; 383,84</t>
+          <t>-33,86; 379,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 10,58</t>
+          <t>-100,0; -13,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-62,72; 180,21</t>
+          <t>-52,79; 217,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-92,36; 61,61</t>
+          <t>-89,79; 51,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,87; 47,94</t>
+          <t>-95,71; 44,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,26; 135,19</t>
+          <t>-42,07; 135,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,47; 100,52</t>
+          <t>-51,77; 84,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-95,48; -28,06</t>
+          <t>-94,8; -32,94</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 1,97</t>
+          <t>-11,03; 1,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 8,43</t>
+          <t>-5,47; 7,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,38; -1,04</t>
+          <t>-13,01; -1,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 3,51</t>
+          <t>-7,48; 4,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 11,84</t>
+          <t>-1,08; 11,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 1,38</t>
+          <t>-8,95; 2,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 0,85</t>
+          <t>-7,26; 1,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 8,41</t>
+          <t>-1,32; 7,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,16; -1,09</t>
+          <t>-9,45; -1,19</t>
         </is>
       </c>
     </row>
@@ -999,54 +999,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-79,22; 32,49</t>
+          <t>-78,2; 30,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,68; 117,44</t>
+          <t>-42,81; 106,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-89,19; -8,69</t>
+          <t>-89,2; -10,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-72,42; 75,04</t>
+          <t>-72,82; 104,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 236,45</t>
+          <t>-12,67; 284,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-89,75; 52,82</t>
+          <t>-88,29; 88,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,95; 20,12</t>
+          <t>-64,81; 18,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 126,54</t>
+          <t>-13,1; 121,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-81,85; -8,92</t>
+          <t>-81,92; -11,59</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 11,41</t>
+          <t>-8,32; 11,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 2,67</t>
+          <t>-15,58; 2,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 7,42</t>
+          <t>-11,17; 7,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 13,64</t>
+          <t>-5,92; 14,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 3,77</t>
+          <t>-13,48; 3,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,19; 3,08</t>
+          <t>-14,32; 3,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 10,06</t>
+          <t>-3,49; 10,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 0,62</t>
+          <t>-11,09; 1,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 2,74</t>
+          <t>-10,44; 2,35</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,68; 143,37</t>
+          <t>-49,63; 149,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-84,25; 39,78</t>
+          <t>-81,74; 53,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-67,11; 116,02</t>
+          <t>-66,03; 107,7</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-28,82; 156,77</t>
+          <t>-32,05; 173,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,84; 54,53</t>
+          <t>-75,61; 35,46</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-79,51; 45,32</t>
+          <t>-77,86; 46,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 115,5</t>
+          <t>-22,75; 106,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,48; 8,03</t>
+          <t>-68,61; 14,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-60,01; 31,49</t>
+          <t>-66,02; 25,34</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-26,56; -9,92</t>
+          <t>-26,66; -9,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-22,13; -3,43</t>
+          <t>-20,72; -3,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,49; -3,49</t>
+          <t>-22,15; -2,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,77; -3,27</t>
+          <t>-17,02; -2,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 9,43</t>
+          <t>-7,73; 9,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 2,74</t>
+          <t>-14,72; 4,47</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-19,48; -8,33</t>
+          <t>-19,27; -8,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 1,02</t>
+          <t>-11,73; 0,46</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,91; -2,73</t>
+          <t>-15,44; -2,69</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-95,53; -53,97</t>
+          <t>-95,57; -51,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-81,19; -19,96</t>
+          <t>-79,66; -16,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-83,76; -16,74</t>
+          <t>-82,52; -8,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-94,06; -20,77</t>
+          <t>-94,6; -22,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-49,51; 104,16</t>
+          <t>-47,33; 108,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,46; 41,4</t>
+          <t>-87,33; 77,9</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-92,26; -60,04</t>
+          <t>-91,95; -59,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-59,95; 9,17</t>
+          <t>-58,95; 4,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-78,53; -8,71</t>
+          <t>-79,18; -18,59</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 9,5</t>
+          <t>-6,78; 10,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,13; -1,55</t>
+          <t>-13,11; -1,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 4,39</t>
+          <t>-9,56; 4,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 11,2</t>
+          <t>-1,56; 11,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 2,51</t>
+          <t>-4,96; 2,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,06; 17,01</t>
+          <t>1,4; 17,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 8,35</t>
+          <t>-2,42; 8,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,13; -0,13</t>
+          <t>-7,0; 0,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 8,64</t>
+          <t>-1,5; 9,04</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-58,31; 755,45</t>
+          <t>-63,35; 789,91</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,14 +1687,14 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-51,23; 756,52</t>
+          <t>-46,03; 792,35</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 16,0</t>
+          <t>-9,83; 13,63</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-25,56; -7,07</t>
+          <t>-25,3; -6,43</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3,39; 30,82</t>
+          <t>4,26; 30,97</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 16,74</t>
+          <t>-6,37; 16,15</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-25,45; -9,0</t>
+          <t>-25,62; -10,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,07; 27,64</t>
+          <t>2,29; 27,31</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 11,3</t>
+          <t>-5,51; 11,57</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-22,87; -10,85</t>
+          <t>-22,41; -10,6</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6,75; 25,37</t>
+          <t>6,08; 25,7</t>
         </is>
       </c>
     </row>
@@ -1863,54 +1863,54 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-39,78; 132,59</t>
+          <t>-42,12; 110,73</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -30,17</t>
+          <t>-100,0; -27,27</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6,97; 264,49</t>
+          <t>18,2; 259,83</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-31,76; 130,15</t>
+          <t>-29,61; 121,11</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -64,64</t>
+          <t>-100,0; -35,51</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,95; 215,85</t>
+          <t>5,8; 205,68</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-24,38; 78,3</t>
+          <t>-25,22; 79,94</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-97,26; -68,72</t>
+          <t>-97,21; -70,64</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>27,28; 177,68</t>
+          <t>27,2; 182,99</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 12,18</t>
+          <t>-1,76; 11,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 4,18</t>
+          <t>-8,91; 3,41</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 1,44</t>
+          <t>-10,56; 1,1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,45; 12,81</t>
+          <t>-0,24; 12,81</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 8,04</t>
+          <t>-4,37; 7,83</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 5,85</t>
+          <t>-5,92; 6,21</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,0; 10,67</t>
+          <t>1,01; 10,59</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 4,19</t>
+          <t>-4,68; 3,8</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 1,95</t>
+          <t>-6,28; 1,93</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 131,73</t>
+          <t>-14,24; 139,56</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-58,55; 50,15</t>
+          <t>-59,5; 44,08</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-69,89; 24,33</t>
+          <t>-72,39; 16,28</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2,32; 203,1</t>
+          <t>-5,23; 203,89</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-31,75; 131,84</t>
+          <t>-36,58; 119,86</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-47,53; 94,66</t>
+          <t>-50,21; 95,74</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,95; 123,57</t>
+          <t>6,85; 124,47</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 52,6</t>
+          <t>-38,09; 44,95</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-49,58; 24,83</t>
+          <t>-49,88; 23,43</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 4,04</t>
+          <t>-5,27; 3,72</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 10,11</t>
+          <t>-0,17; 10,58</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 10,6</t>
+          <t>-1,02; 10,16</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 6,46</t>
+          <t>-2,52; 6,56</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 9,39</t>
+          <t>-0,12; 9,31</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,93; 18,75</t>
+          <t>5,46; 17,57</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 3,94</t>
+          <t>-2,63; 3,85</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,28</t>
+          <t>1,2; 8,47</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4,01; 12,73</t>
+          <t>4,21; 12,82</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-55,55; 83,25</t>
+          <t>-55,01; 76,79</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 189,44</t>
+          <t>-6,75; 211,48</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 198,49</t>
+          <t>-13,85; 186,5</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-35,27; 149,94</t>
+          <t>-30,33; 157,81</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 217,89</t>
+          <t>-3,18; 217,63</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>57,81; 417,74</t>
+          <t>68,1; 414,46</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-31,48; 73,82</t>
+          <t>-31,54; 69,64</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>9,7; 152,95</t>
+          <t>12,15; 157,7</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>46,54; 232,34</t>
+          <t>46,93; 229,5</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,46</t>
+          <t>-3,89; 1,39</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 0,3</t>
+          <t>-5,03; 0,35</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 0,12</t>
+          <t>-5,42; 0,13</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 4,03</t>
+          <t>-0,95; 4,03</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,26</t>
+          <t>-2,63; 2,27</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,22</t>
+          <t>-1,55; 4,02</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,11</t>
+          <t>-1,71; 2,16</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,66</t>
+          <t>-2,89; 0,72</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,4</t>
+          <t>-2,42; 1,6</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-30,1; 14,37</t>
+          <t>-29,57; 13,56</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 3,48</t>
+          <t>-38,31; 3,7</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-40,98; 1,04</t>
+          <t>-40,96; 1,95</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 47,33</t>
+          <t>-9,37; 48,77</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-25,15; 27,52</t>
+          <t>-24,73; 26,08</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 49,2</t>
+          <t>-14,46; 47,72</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 21,92</t>
+          <t>-15,15; 22,32</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 7,18</t>
+          <t>-25,35; 7,38</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-21,77; 14,29</t>
+          <t>-21,33; 16,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP26C_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 11,44</t>
+          <t>-5,94; 12,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 15,63</t>
+          <t>-3,82; 16,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,84; -2,48</t>
+          <t>-14,88; -2,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 11,1</t>
+          <t>-8,99; 9,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,77; 1,92</t>
+          <t>-14,02; 1,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 0,46</t>
+          <t>-15,37; -0,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 8,46</t>
+          <t>-4,81; 8,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 5,2</t>
+          <t>-6,59; 5,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,96; -2,84</t>
+          <t>-12,61; -2,66</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-48,91; 266,85</t>
+          <t>-52,0; 361,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 379,26</t>
+          <t>-31,68; 446,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -13,63</t>
+          <t>-100,0; 52,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-52,79; 217,43</t>
+          <t>-62,37; 176,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-89,79; 51,29</t>
+          <t>-91,21; 66,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,71; 44,04</t>
+          <t>-94,15; 42,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,07; 135,83</t>
+          <t>-39,71; 148,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-51,77; 84,77</t>
+          <t>-52,11; 98,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-94,8; -32,94</t>
+          <t>-94,37; -29,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 1,66</t>
+          <t>-11,3; 1,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 7,83</t>
+          <t>-5,85; 8,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,01; -1,19</t>
+          <t>-12,78; -1,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 4,0</t>
+          <t>-7,19; 3,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 11,83</t>
+          <t>-1,5; 12,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 2,04</t>
+          <t>-8,95; 1,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 1,05</t>
+          <t>-7,36; 1,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 7,9</t>
+          <t>-1,08; 8,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,45; -1,19</t>
+          <t>-9,24; -1,36</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-78,2; 30,17</t>
+          <t>-79,08; 35,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,81; 106,84</t>
+          <t>-42,4; 134,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-89,2; -10,1</t>
+          <t>-90,23; -9,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-72,82; 104,05</t>
+          <t>-69,09; 98,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 284,58</t>
+          <t>-16,68; 248,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,29; 88,48</t>
+          <t>-89,34; 57,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-64,81; 18,9</t>
+          <t>-65,28; 23,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 121,3</t>
+          <t>-10,13; 122,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-81,92; -11,59</t>
+          <t>-83,12; -9,11</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 11,2</t>
+          <t>-8,03; 12,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 2,03</t>
+          <t>-14,48; 2,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 7,71</t>
+          <t>-11,7; 6,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 14,69</t>
+          <t>-5,02; 14,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 3,08</t>
+          <t>-13,36; 3,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 3,02</t>
+          <t>-14,81; 3,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 10,02</t>
+          <t>-3,97; 10,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 1,07</t>
+          <t>-11,67; 0,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 2,35</t>
+          <t>-10,75; 2,01</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-49,63; 149,6</t>
+          <t>-47,03; 169,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-81,74; 53,35</t>
+          <t>-82,96; 52,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,03; 107,7</t>
+          <t>-66,09; 88,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-32,05; 173,33</t>
+          <t>-31,18; 165,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-75,61; 35,46</t>
+          <t>-77,8; 44,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-77,86; 46,96</t>
+          <t>-81,07; 43,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 106,34</t>
+          <t>-24,91; 110,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,61; 14,24</t>
+          <t>-70,91; 18,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,02; 25,34</t>
+          <t>-65,34; 21,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-26,66; -9,34</t>
+          <t>-26,42; -9,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-20,72; -3,12</t>
+          <t>-20,85; -2,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,15; -2,87</t>
+          <t>-22,31; -3,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,02; -2,64</t>
+          <t>-17,01; -3,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 9,53</t>
+          <t>-8,72; 9,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 4,47</t>
+          <t>-14,45; 3,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-19,27; -8,42</t>
+          <t>-19,66; -8,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 0,46</t>
+          <t>-12,56; 0,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,44; -2,69</t>
+          <t>-16,81; -3,33</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-95,57; -51,59</t>
+          <t>-95,75; -50,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-79,66; -16,32</t>
+          <t>-80,14; -13,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-82,52; -8,49</t>
+          <t>-83,52; -17,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-94,6; -22,32</t>
+          <t>-94,07; -21,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,33; 108,4</t>
+          <t>-51,99; 111,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,33; 77,9</t>
+          <t>-92,05; 43,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-91,95; -59,83</t>
+          <t>-91,94; -59,22</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 4,23</t>
+          <t>-60,93; 8,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-79,18; -18,59</t>
+          <t>-80,81; -20,02</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 10,73</t>
+          <t>-6,66; 10,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,11; -1,53</t>
+          <t>-12,95; -1,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 4,37</t>
+          <t>-9,43; 4,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 11,15</t>
+          <t>-1,67; 11,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 2,52</t>
+          <t>-6,1; 2,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 17,55</t>
+          <t>1,45; 17,12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 8,27</t>
+          <t>-2,17; 8,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 0,15</t>
+          <t>-6,63; -0,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 9,04</t>
+          <t>-1,19; 8,95</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-63,35; 789,91</t>
+          <t>-49,9; 675,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-46,03; 792,35</t>
+          <t>-44,49; 896,17</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 13,63</t>
+          <t>-10,61; 14,77</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-25,3; -6,43</t>
+          <t>-27,37; -7,49</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,26; 30,97</t>
+          <t>1,43; 31,06</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 16,15</t>
+          <t>-7,03; 15,83</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-25,62; -10,07</t>
+          <t>-26,8; -10,13</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,29; 27,31</t>
+          <t>0,88; 27,23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 11,57</t>
+          <t>-5,23; 11,6</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-22,41; -10,6</t>
+          <t>-22,69; -10,24</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6,08; 25,7</t>
+          <t>5,96; 24,98</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-42,12; 110,73</t>
+          <t>-45,32; 120,56</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -27,27</t>
+          <t>-100,0; -44,33</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18,2; 259,83</t>
+          <t>5,4; 253,41</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-29,61; 121,11</t>
+          <t>-30,11; 118,26</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -35,51</t>
+          <t>-100,0; -55,13</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,8; 205,68</t>
+          <t>4,84; 220,08</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-25,22; 79,94</t>
+          <t>-23,99; 79,95</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-97,21; -70,64</t>
+          <t>-97,21; -67,26</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>27,2; 182,99</t>
+          <t>22,62; 167,61</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 11,87</t>
+          <t>-2,73; 12,14</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 3,41</t>
+          <t>-9,27; 2,92</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 1,1</t>
+          <t>-10,99; 1,4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 12,81</t>
+          <t>-0,11; 12,68</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 7,83</t>
+          <t>-3,93; 8,17</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 6,21</t>
+          <t>-6,17; 5,63</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,01; 10,59</t>
+          <t>1,45; 10,51</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 3,8</t>
+          <t>-4,72; 3,66</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 1,93</t>
+          <t>-6,39; 2,04</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 139,56</t>
+          <t>-17,61; 145,76</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-59,5; 44,08</t>
+          <t>-61,05; 33,48</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-72,39; 16,28</t>
+          <t>-69,04; 21,98</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 203,89</t>
+          <t>-3,3; 191,77</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-36,58; 119,86</t>
+          <t>-34,59; 132,54</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-50,21; 95,74</t>
+          <t>-51,71; 92,52</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,85; 124,47</t>
+          <t>10,04; 125,93</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-38,09; 44,95</t>
+          <t>-37,61; 43,8</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-49,88; 23,43</t>
+          <t>-49,1; 25,87</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 3,72</t>
+          <t>-5,37; 4,13</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 10,58</t>
+          <t>-0,54; 10,39</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 10,16</t>
+          <t>-0,81; 10,64</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 6,56</t>
+          <t>-1,96; 6,85</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 9,31</t>
+          <t>-0,01; 9,68</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,46; 17,57</t>
+          <t>5,96; 17,95</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 3,85</t>
+          <t>-2,43; 4,18</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,2; 8,47</t>
+          <t>1,04; 8,36</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4,21; 12,82</t>
+          <t>4,37; 13,05</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-55,01; 76,79</t>
+          <t>-55,0; 82,66</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 211,48</t>
+          <t>-8,5; 194,84</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 186,5</t>
+          <t>-12,09; 194,65</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-30,33; 157,81</t>
+          <t>-25,37; 165,99</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 217,63</t>
+          <t>-4,04; 227,64</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>68,1; 414,46</t>
+          <t>61,93; 405,92</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-31,54; 69,64</t>
+          <t>-29,72; 78,94</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>12,15; 157,7</t>
+          <t>10,25; 151,76</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>46,93; 229,5</t>
+          <t>49,66; 242,96</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 1,39</t>
+          <t>-3,71; 1,52</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 0,35</t>
+          <t>-5,14; 0,45</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 0,13</t>
+          <t>-5,2; 0,31</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,03</t>
+          <t>-1,0; 4,33</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,27</t>
+          <t>-2,79; 2,5</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 4,02</t>
+          <t>-1,51; 4,2</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,16</t>
+          <t>-1,65; 2,05</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,72</t>
+          <t>-3,1; 0,6</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 1,6</t>
+          <t>-2,43; 1,61</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 13,56</t>
+          <t>-29,2; 15,52</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 3,7</t>
+          <t>-39,1; 4,48</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-40,96; 1,95</t>
+          <t>-41,57; 2,82</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 48,77</t>
+          <t>-9,46; 54,61</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-24,73; 26,08</t>
+          <t>-25,32; 30,91</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 47,72</t>
+          <t>-14,51; 50,73</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 22,32</t>
+          <t>-14,4; 21,31</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-25,35; 7,38</t>
+          <t>-26,79; 6,39</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-21,33; 16,89</t>
+          <t>-21,09; 16,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP26C_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP26C_R-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,47 +624,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,06</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-5,54</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-6,6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,82</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,65</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-7,59</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,06</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-5,54</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>-7,38</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,88</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>-0,28</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>-6,97</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,88</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-0,28</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>-7,29</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 12,52</t>
+          <t>-8,29; 10,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 16,03</t>
+          <t>-14,24; 1,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,88; -2,2</t>
+          <t>-15,04; 0,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 9,76</t>
+          <t>-6,14; 13,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 1,78</t>
+          <t>-2,45; 16,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,37; -0,08</t>
+          <t>-13,94; -1,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 8,37</t>
+          <t>-5,18; 8,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 5,9</t>
+          <t>-6,44; 5,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,61; -2,66</t>
+          <t>-12,44; -2,07</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,59%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-55,11%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-65,6%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>33,12%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>66,44%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-89,28%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-55,11%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-69,35%</t>
+          <t>-86,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-78,14%</t>
+          <t>-74,66%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-52,0; 361,29</t>
+          <t>-62,72; 180,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,68; 446,99</t>
+          <t>-92,36; 61,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 52,93</t>
+          <t>-97,5; 71,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 176,39</t>
+          <t>-52,48; 293,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,21; 66,87</t>
+          <t>-28,13; 383,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-94,15; 42,31</t>
+          <t>-100,0; 50,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,71; 148,94</t>
+          <t>-43,26; 135,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-52,11; 98,25</t>
+          <t>-52,47; 100,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-94,37; -29,98</t>
+          <t>-94,7; -11,36</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,76</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,22</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-3,49</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-4,5</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,16</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-6,73</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,76</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,22</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,67</t>
+          <t>-5,56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,15</t>
+          <t>-4,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 1,78</t>
+          <t>-7,23; 3,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 8,66</t>
+          <t>-0,94; 11,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,78; -1,05</t>
+          <t>-8,76; 1,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 3,95</t>
+          <t>-10,73; 1,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 12,01</t>
+          <t>-6,09; 8,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 1,82</t>
+          <t>-11,59; 0,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 1,22</t>
+          <t>-7,45; 0,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 8,2</t>
+          <t>-1,6; 8,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -1,36</t>
+          <t>-8,57; -0,34</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-23,76%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70,37%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-47,1%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-43,37%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>11,15%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-64,83%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-23,76%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>70,37%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-49,46%</t>
+          <t>-53,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-58,18%</t>
+          <t>-51,01%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-79,08; 35,84</t>
+          <t>-72,42; 75,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,4; 134,72</t>
+          <t>-15,05; 236,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-90,23; -9,32</t>
+          <t>-89,17; 60,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-69,09; 98,88</t>
+          <t>-79,22; 32,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,68; 248,48</t>
+          <t>-41,68; 117,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-89,34; 57,67</t>
+          <t>-83,52; 16,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-65,28; 23,57</t>
+          <t>-65,95; 20,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 122,3</t>
+          <t>-16,07; 126,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-83,12; -9,11</t>
+          <t>-78,36; 2,12</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,26</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-5,18</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-6,26</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>1,39</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-5,82</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,3</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,26</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-5,18</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-5,59</t>
+          <t>-2,21</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,04</t>
+          <t>-4,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 12,17</t>
+          <t>-4,75; 13,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 2,47</t>
+          <t>-13,13; 3,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 6,67</t>
+          <t>-14,72; 1,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 14,91</t>
+          <t>-8,06; 11,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 3,36</t>
+          <t>-14,43; 2,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,81; 3,31</t>
+          <t>-11,57; 7,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 10,12</t>
+          <t>-2,95; 10,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 0,9</t>
+          <t>-11,28; 0,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 2,01</t>
+          <t>-9,89; 2,17</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>31,61%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-38,48%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-46,49%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>10,98%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-46,01%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-18,21%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>31,61%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-38,48%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-41,5%</t>
+          <t>-17,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-30,92%</t>
+          <t>-32,77%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,03; 169,14</t>
+          <t>-28,82; 156,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-82,96; 52,48</t>
+          <t>-73,84; 54,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,09; 88,07</t>
+          <t>-80,93; 29,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,18; 165,36</t>
+          <t>-47,68; 143,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,8; 44,83</t>
+          <t>-84,25; 39,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,07; 43,02</t>
+          <t>-66,58; 108,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,91; 110,27</t>
+          <t>-18,68; 115,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,91; 18,1</t>
+          <t>-70,48; 8,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,34; 21,89</t>
+          <t>-61,04; 26,05</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-9,68</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,64</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-5,7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-17,82</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-12,25</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-12,97</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-9,68</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,64</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,05</t>
+          <t>-12,74</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-9,45</t>
+          <t>-9,13</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-26,42; -9,64</t>
+          <t>-16,77; -3,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-20,85; -2,95</t>
+          <t>-7,85; 9,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-22,31; -3,99</t>
+          <t>-14,16; 4,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,01; -3,49</t>
+          <t>-26,56; -9,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 9,32</t>
+          <t>-22,13; -3,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 3,01</t>
+          <t>-21,97; -3,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-19,66; -8,35</t>
+          <t>-19,48; -8,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 0,54</t>
+          <t>-12,24; 1,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-16,81; -3,33</t>
+          <t>-15,7; -2,0</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-76,45%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-45,02%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-83,62%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-57,5%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-60,86%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-76,45%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-47,77%</t>
+          <t>-59,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-55,98%</t>
+          <t>-54,07%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-95,75; -50,5</t>
+          <t>-94,06; -20,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-80,14; -13,94</t>
+          <t>-49,51; 104,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-83,52; -17,13</t>
+          <t>-86,26; 53,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-94,07; -21,58</t>
+          <t>-95,53; -53,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-51,99; 111,25</t>
+          <t>-81,19; -19,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-92,05; 43,34</t>
+          <t>-83,36; -16,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-91,94; -59,22</t>
+          <t>-92,26; -60,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-60,93; 8,07</t>
+          <t>-59,95; 9,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-80,81; -20,02</t>
+          <t>-77,64; -4,97</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4,15</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,29</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>8,09</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,9</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-4,84</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,85</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,15</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,29</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,24</t>
+          <t>-2,08</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>3,23</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 10,5</t>
+          <t>-1,6; 11,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,95; -1,53</t>
+          <t>-4,85; 2,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 4,36</t>
+          <t>1,57; 16,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 11,63</t>
+          <t>-6,24; 9,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 2,53</t>
+          <t>-13,13; -1,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 17,12</t>
+          <t>-9,8; 3,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 8,61</t>
+          <t>-2,45; 8,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,63; -0,12</t>
+          <t>-7,13; -0,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 8,95</t>
+          <t>-2,21; 8,2</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>270,61%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-18,64%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>528,28%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>18,6%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-38,24%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>270,61%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-18,64%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>537,68%</t>
+          <t>-42,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>111,82%</t>
+          <t>102,82%</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-49,9; 675,29</t>
+          <t>-58,31; 755,45</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-44,49; 896,17</t>
+          <t>-51,96; 731,98</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>4,76</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-16,95</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>13,26</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>2,12</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-15,83</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>17,41</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>4,76</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-16,95</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,35</t>
+          <t>16,21</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15,72</t>
+          <t>14,68</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 14,77</t>
+          <t>-6,57; 16,74</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-27,37; -7,49</t>
+          <t>-25,45; -9,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,43; 31,06</t>
+          <t>0,99; 26,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 15,83</t>
+          <t>-9,15; 16,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-26,8; -10,13</t>
+          <t>-25,56; -7,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,88; 27,23</t>
+          <t>2,49; 29,83</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 11,6</t>
+          <t>-5,48; 11,3</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-22,69; -10,24</t>
+          <t>-22,87; -10,85</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,96; 24,98</t>
+          <t>5,74; 24,05</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>26,14%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-92,98%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>72,74%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>11,51%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-86,18%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>94,72%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>26,14%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-92,98%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>80,24%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-45,32; 120,56</t>
+          <t>-31,76; 130,15</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -44,33</t>
+          <t>-100,0; -64,64</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>5,4; 253,41</t>
+          <t>1,47; 210,84</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 118,26</t>
+          <t>-39,78; 132,59</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -55,13</t>
+          <t>-100,0; -30,17</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,84; 220,08</t>
+          <t>5,56; 254,84</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 79,95</t>
+          <t>-24,38; 78,3</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-97,21; -67,26</t>
+          <t>-97,26; -68,72</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>22,62; 167,61</t>
+          <t>23,25; 168,58</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>6,15</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1,87</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>4,98</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-2,7</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-4,62</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>6,15</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>1,87</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>-4,41</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,11</t>
+          <t>-1,46</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 12,14</t>
+          <t>0,45; 12,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 2,92</t>
+          <t>-3,61; 8,04</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-10,99; 1,4</t>
+          <t>-4,54; 7,35</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 12,68</t>
+          <t>-2,32; 12,18</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 8,17</t>
+          <t>-8,72; 4,18</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 5,63</t>
+          <t>-11,33; 1,84</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,45; 10,51</t>
+          <t>1,0; 10,67</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 3,66</t>
+          <t>-4,59; 4,19</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 2,04</t>
+          <t>-5,9; 2,83</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>66,05%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>20,09%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>12,93%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>41,86%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-22,71%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-38,83%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>66,05%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>20,09%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>-37,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-19,97%</t>
+          <t>-13,84%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 145,76</t>
+          <t>2,32; 203,1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-61,05; 33,48</t>
+          <t>-31,75; 131,84</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-69,04; 21,98</t>
+          <t>-38,59; 118,95</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 191,77</t>
+          <t>-16,48; 131,73</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-34,59; 132,54</t>
+          <t>-58,55; 50,15</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-51,71; 92,52</t>
+          <t>-68,91; 27,19</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,04; 125,93</t>
+          <t>5,95; 123,57</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-37,61; 43,8</t>
+          <t>-34,96; 52,6</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-49,1; 25,87</t>
+          <t>-45,99; 34,81</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>4,51</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>11,9</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-0,55</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>5,02</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>4,59</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>4,51</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,69</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>8,41</t>
+          <t>8,57</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 4,13</t>
+          <t>-2,93; 6,46</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 10,39</t>
+          <t>-0,6; 9,39</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 10,64</t>
+          <t>5,99; 19,28</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 6,85</t>
+          <t>-5,34; 4,04</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 9,68</t>
+          <t>-0,48; 10,11</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,96; 17,95</t>
+          <t>-0,61; 11,13</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 4,18</t>
+          <t>-2,63; 3,94</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,36</t>
+          <t>0,91; 8,28</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4,37; 13,05</t>
+          <t>4,17; 13,02</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>33,96%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>71,75%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>189,42%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-7,26%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>66,51%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>60,85%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>33,96%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>71,75%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>186,07%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>121,73%</t>
+          <t>124,03%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-55,0; 82,66</t>
+          <t>-35,27; 149,94</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 194,84</t>
+          <t>-10,74; 217,89</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 194,65</t>
+          <t>59,98; 428,31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-25,37; 165,99</t>
+          <t>-55,55; 83,25</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 227,64</t>
+          <t>-13,73; 189,44</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>61,93; 405,92</t>
+          <t>-9,5; 204,52</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-29,72; 78,94</t>
+          <t>-31,48; 73,82</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>10,25; 151,76</t>
+          <t>9,7; 152,95</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>49,66; 242,96</t>
+          <t>49,59; 235,55</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>1,48</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-0,14</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1,86</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-1,21</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-2,22</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-2,63</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>1,48</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>-1,94</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,52</t>
+          <t>-0,86; 4,03</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 0,45</t>
+          <t>-2,58; 2,26</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 0,31</t>
+          <t>-0,96; 4,58</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,33</t>
+          <t>-3,92; 1,46</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 2,5</t>
+          <t>-4,95; 0,3</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 4,2</t>
+          <t>-4,38; 0,96</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,05</t>
+          <t>-1,77; 2,11</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,6</t>
+          <t>-3,12; 0,66</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,61</t>
+          <t>-1,78; 2,0</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>15,66%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-1,47%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-10,45%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-19,08%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-22,62%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-1,47%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>-16,67%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-4,78%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-29,2; 15,52</t>
+          <t>-9,16; 47,33</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 4,48</t>
+          <t>-25,15; 27,52</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-41,57; 2,82</t>
+          <t>-8,54; 55,23</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 54,61</t>
+          <t>-30,1; 14,37</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-25,32; 30,91</t>
+          <t>-38,25; 3,48</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 50,73</t>
+          <t>-34,64; 9,61</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 21,31</t>
+          <t>-15,13; 21,92</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 6,39</t>
+          <t>-26,87; 7,18</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-21,09; 16,77</t>
+          <t>-15,68; 20,62</t>
         </is>
       </c>
     </row>
